--- a/evaluation/evaluation.xlsx
+++ b/evaluation/evaluation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LEXICLEAR\LexiClear\evaluation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD5E3CE-D584-4969-9461-14514EF22A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{866DEEE3-5927-49D2-A1A9-85CF433D9152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{41FE13FA-1381-4F87-B643-E73B9790CDD3}"/>
   </bookViews>
@@ -31,151 +31,151 @@
     <t>Can the company transfer the employee to another branch?</t>
   </si>
   <si>
-    <t>Yes. The company may transfer the employee to any branch or sister concern in India or outside India.</t>
-  </si>
-  <si>
-    <t>Can the employee be required to work outside company premises?</t>
-  </si>
-  <si>
-    <t>Yes. The employee may be required to work at premises other than the company premises.</t>
-  </si>
-  <si>
-    <t>Who assigns duties to the employee?</t>
-  </si>
-  <si>
-    <t>The Director of the Company or the immediate senior assigns duties.</t>
-  </si>
-  <si>
-    <t>Should the employee follow company policies?</t>
-  </si>
-  <si>
-    <t>Yes. The employee must follow company policies and applicable laws.</t>
-  </si>
-  <si>
     <t>Can the employee sign company documents without written consent?</t>
   </si>
   <si>
-    <t>No. The employee cannot sign documents on behalf of the company without written consent.</t>
-  </si>
-  <si>
-    <t>Who owns intellectual property created during employment?</t>
-  </si>
-  <si>
-    <t>The company owns all intellectual property created during employment.</t>
-  </si>
-  <si>
     <t>Can the employee disclose confidential company information?</t>
   </si>
   <si>
-    <t>No. The employee must keep confidential information confidential during and after employment.</t>
-  </si>
-  <si>
-    <t>Should the employee return company documents after termination?</t>
-  </si>
-  <si>
-    <t>Yes. All company documents and property must be returned after termination.</t>
-  </si>
-  <si>
-    <t>How long is the non-compete period?</t>
-  </si>
-  <si>
-    <t>Three years after employment.</t>
-  </si>
-  <si>
-    <t>Can the employee contact company clients after leaving the company?</t>
-  </si>
-  <si>
-    <t>No. The employee must not directly or indirectly contact company clients.</t>
-  </si>
-  <si>
-    <t>Can the employer terminate the employee immediately?</t>
-  </si>
-  <si>
-    <t>Yes. The employer may terminate employment immediately without notice.</t>
-  </si>
-  <si>
-    <t>What is the penalty for breaking the two-year bond?</t>
-  </si>
-  <si>
-    <t>The employee must pay a penalty of Rs. 2 lakhs.</t>
-  </si>
-  <si>
-    <t>Can the company recover training expenses?</t>
-  </si>
-  <si>
-    <t>Yes. If the employee resigns before completing six months of training.</t>
-  </si>
-  <si>
-    <t>Can the company recover damages if the employee commits fraud?</t>
-  </si>
-  <si>
-    <t>Yes. The company may recover damages through legal proceedings.</t>
-  </si>
-  <si>
-    <t>Is severance pay always provided?</t>
-  </si>
-  <si>
-    <t>No. Severance pay is not provided in cases specified in the agreement.</t>
-  </si>
-  <si>
-    <t>What happens if the employee violates company rules?</t>
-  </si>
-  <si>
-    <t>The employee may face disciplinary action or termination.</t>
-  </si>
-  <si>
-    <t>Can the agreement be amended?</t>
-  </si>
-  <si>
-    <t>Yes. It may be amended by mutual agreement of both parties.</t>
-  </si>
-  <si>
-    <t>Which law governs the employment agreement?</t>
-  </si>
-  <si>
-    <t>The laws of Jaipur</t>
-  </si>
-  <si>
-    <t>Where will arbitration proceedings be conducted?</t>
-  </si>
-  <si>
-    <t>Jaipur.</t>
-  </si>
-  <si>
-    <t>Who conducts arbitration?</t>
-  </si>
-  <si>
-    <t>A single arbitrator appointed as specified in the agreement.</t>
-  </si>
-  <si>
     <t>Can the company modify its rules and regulations?</t>
   </si>
   <si>
-    <t>Yes. The company may modify its rules and regulations from time to time.</t>
-  </si>
-  <si>
-    <t>Does the agreement supersede previous agreements?</t>
-  </si>
-  <si>
-    <t>Yes. It supersedes previous oral and written agreements.</t>
-  </si>
-  <si>
-    <t>Can confidential information be used for personal benefit?</t>
-  </si>
-  <si>
-    <t>No. Confidential information cannot be used for personal benefit or disclosed.</t>
-  </si>
-  <si>
-    <t>Can the company terminate employment for misconduct?</t>
-  </si>
-  <si>
-    <t>Yes. Misconduct is a valid ground for termination.</t>
-  </si>
-  <si>
-    <t>Can the employee work for a competing company after leaving?</t>
-  </si>
-  <si>
-    <t>No. The employee cannot compete for three years after employment.</t>
+    <t>What position is the employee appointed to?</t>
+  </si>
+  <si>
+    <t>How long is the probationary period?</t>
+  </si>
+  <si>
+    <t>Can the company extend the probationary period?</t>
+  </si>
+  <si>
+    <t>Where is the employee initially stationed?</t>
+  </si>
+  <si>
+    <t>Can the employee be required to work outside the company's premises?</t>
+  </si>
+  <si>
+    <t>Who can assign duties and responsibilities to the employee?</t>
+  </si>
+  <si>
+    <t>Must the employee follow company policies and applicable laws?</t>
+  </si>
+  <si>
+    <t>Where will arbitration proceedings be held?</t>
+  </si>
+  <si>
+    <t>Who is appointed as the sole arbitrator?</t>
+  </si>
+  <si>
+    <t>In which language will the arbitration proceedings be conducted?</t>
+  </si>
+  <si>
+    <t>What is the employee's annual CTC?</t>
+  </si>
+  <si>
+    <t>Who owns intellectual property created by the employee during employment?</t>
+  </si>
+  <si>
+    <t>What must the employee do with company documents after termination?</t>
+  </si>
+  <si>
+    <t>How long does the non-compete restriction apply after employment?</t>
+  </si>
+  <si>
+    <t>Can the employee directly or indirectly contact the company's clients after employment?</t>
+  </si>
+  <si>
+    <t>What notice must the employee give to terminate the employment agreement?</t>
+  </si>
+  <si>
+    <t>Can the employer terminate the employee immediately without notice?</t>
+  </si>
+  <si>
+    <t>What is the penalty for leaving the company before completing two years?</t>
+  </si>
+  <si>
+    <t>Can the company recover training expenses if the employee resigns early?</t>
+  </si>
+  <si>
+    <t>Is severance pay provided if the employee is terminated for breach of the agreement or failure to meet performance criteria?</t>
+  </si>
+  <si>
+    <t>What law governs the employment agreement?</t>
+  </si>
+  <si>
+    <t>The employee is appointed as a Senior Software Engineer.</t>
+  </si>
+  <si>
+    <t>The probationary period is 6 months.</t>
+  </si>
+  <si>
+    <t>Yes. The company may extend the probationary period at its sole discretion if the employee has not completed the full probationary period or their performance has not met expectations.</t>
+  </si>
+  <si>
+    <t>The employee is initially stationed at the Employer's offices in Mangaluru.</t>
+  </si>
+  <si>
+    <t>Yes. The company may transfer the employee to any existing or future branch or sister concern in India or outside India.</t>
+  </si>
+  <si>
+    <t>Yes. The employee may be required to work at premises other than the company's premises from time to time.</t>
+  </si>
+  <si>
+    <t>Duties and responsibilities may be assigned by the Director of the Company, a Manager immediately senior to the Employee, or the Board of Directors.</t>
+  </si>
+  <si>
+    <t>Yes. The employee must follow applicable laws and regulations as well as the Company's policies and instructions.</t>
+  </si>
+  <si>
+    <t>No. The employee cannot sign documents or commit on behalf of the company without written consent and mutual consent.</t>
+  </si>
+  <si>
+    <t>Yes. The Employer can modify the Agreement or the Company's Rules and Regulations from time to time, and the modification applies from the same day.</t>
+  </si>
+  <si>
+    <t>Arbitration proceedings will be held in Jaipur.</t>
+  </si>
+  <si>
+    <t>Mr. Ramesh Chandra, Advocate, is appointed as the sole arbitrator.</t>
+  </si>
+  <si>
+    <t>The arbitration proceedings will be conducted in Hindi.</t>
+  </si>
+  <si>
+    <t>The employee's CTC is Rs. 12,00,000 per annum.</t>
+  </si>
+  <si>
+    <t>No. The employee must not disclose or improperly use confidential information, trade secrets, client information, or other confidential company information during or after employment, except as permitted by the agreement or required by law.</t>
+  </si>
+  <si>
+    <t>The company owns the intellectual property created by the employee during employment, including software, hardware, and the company's source code.</t>
+  </si>
+  <si>
+    <t>The employee must return all company business documentation, software, notes, records, and other company property or materials as required.</t>
+  </si>
+  <si>
+    <t>The agreement states that the employee shall not open a similar-nature company for up to three years after employment.</t>
+  </si>
+  <si>
+    <t>The agreement prohibits the employee from trying to connect directly or indirectly with the company's clients during and after employment.</t>
+  </si>
+  <si>
+    <t>The employee must give the Employer at least 60 days' written notice.</t>
+  </si>
+  <si>
+    <t>Yes. The Employer can terminate the employee at any time with immediate effect without giving a notice period.</t>
+  </si>
+  <si>
+    <t>The employee is liable to pay a penalty of Rs. 2 lakhs.</t>
+  </si>
+  <si>
+    <t>Yes. The company has the right to recover training expenses if the employee resigns before completing 6 months of the training tenure.</t>
+  </si>
+  <si>
+    <t>No. Severance pay will not be provided if the company terminates the employee because of a breach of the agreement or failure to meet the prescribed performance criteria.</t>
+  </si>
+  <si>
+    <t>The employment agreement is governed by and construed in accordance with the laws of Jaipur, India.</t>
   </si>
 </sst>
 </file>
@@ -659,8 +659,14 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1038,212 +1044,216 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69C8EFC1-D9A8-4F72-A691-BE65BD72063A}">
   <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="28.77734375" customWidth="1"/>
+    <col min="2" max="2" width="51.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B10" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="B16" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="B17" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B18" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B19" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B20" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="B21" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B22" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="B23" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B24" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="B25" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="B26" s="2" t="s">
         <v>51</v>
       </c>
     </row>
